--- a/sheets/S08A22P222.xlsx
+++ b/sheets/S08A22P222.xlsx
@@ -36190,7 +36190,7 @@
         <v>13</v>
       </c>
       <c r="G1120" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H1120" t="s">
         <v>15</v>
@@ -36216,7 +36216,7 @@
         <v>13</v>
       </c>
       <c r="G1121" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H1121" t="s">
         <v>15</v>
@@ -36242,7 +36242,7 @@
         <v>13</v>
       </c>
       <c r="G1122" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H1122" t="s">
         <v>15</v>
@@ -36268,7 +36268,7 @@
         <v>13</v>
       </c>
       <c r="G1123" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H1123" t="s">
         <v>15</v>
@@ -36294,7 +36294,7 @@
         <v>13</v>
       </c>
       <c r="G1124" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H1124" t="s">
         <v>15</v>
@@ -36320,7 +36320,7 @@
         <v>13</v>
       </c>
       <c r="G1125" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H1125" t="s">
         <v>15</v>
@@ -36346,7 +36346,7 @@
         <v>13</v>
       </c>
       <c r="G1126" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H1126" t="s">
         <v>15</v>
@@ -36372,7 +36372,7 @@
         <v>13</v>
       </c>
       <c r="G1127" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H1127" t="s">
         <v>15</v>
@@ -36398,7 +36398,7 @@
         <v>13</v>
       </c>
       <c r="G1128" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H1128" t="s">
         <v>15</v>
@@ -36424,7 +36424,7 @@
         <v>13</v>
       </c>
       <c r="G1129" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H1129" t="s">
         <v>15</v>
@@ -36450,7 +36450,7 @@
         <v>13</v>
       </c>
       <c r="G1130" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H1130" t="s">
         <v>15</v>
@@ -36476,7 +36476,7 @@
         <v>13</v>
       </c>
       <c r="G1131" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H1131" t="s">
         <v>15</v>
@@ -36502,7 +36502,7 @@
         <v>13</v>
       </c>
       <c r="G1132" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H1132" t="s">
         <v>15</v>
@@ -36528,7 +36528,7 @@
         <v>13</v>
       </c>
       <c r="G1133" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H1133" t="s">
         <v>15</v>
